--- a/school_2/ceilling/vor_spartac_2_ceilling.xlsx
+++ b/school_2/ceilling/vor_spartac_2_ceilling.xlsx
@@ -4,35 +4,36 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15624" windowHeight="8760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15624" windowHeight="8760" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="6.4ГКЛ" sheetId="22" r:id="rId1"/>
-    <sheet name="6.3инжКом" sheetId="21" r:id="rId2"/>
-    <sheet name="6.2ГКЛ" sheetId="20" r:id="rId3"/>
-    <sheet name="6.1ГКЛ" sheetId="19" r:id="rId4"/>
-    <sheet name="Лист2" sheetId="3" r:id="rId5"/>
-    <sheet name="Лист1" sheetId="1" r:id="rId6"/>
-    <sheet name="5.1ГКЛ" sheetId="18" r:id="rId7"/>
-    <sheet name="Table 1" sheetId="2" r:id="rId8"/>
-    <sheet name="2расчет" sheetId="9" r:id="rId9"/>
-    <sheet name="3вор" sheetId="4" r:id="rId10"/>
-    <sheet name="общая" sheetId="11" r:id="rId11"/>
-    <sheet name="3пом" sheetId="8" r:id="rId12"/>
-    <sheet name="3расчет" sheetId="6" r:id="rId13"/>
-    <sheet name="3.1-Пт" sheetId="14" r:id="rId14"/>
-    <sheet name="3.1" sheetId="15" r:id="rId15"/>
-    <sheet name="4.1-Пт" sheetId="16" r:id="rId16"/>
-    <sheet name="4.1" sheetId="17" r:id="rId17"/>
-    <sheet name="ПТ3эт" sheetId="12" r:id="rId18"/>
-    <sheet name="ПТ2эт" sheetId="13" r:id="rId19"/>
+    <sheet name="6.3инжКом (2)" sheetId="23" r:id="rId1"/>
+    <sheet name="6.4ГКЛ" sheetId="22" r:id="rId2"/>
+    <sheet name="6.3инжКом" sheetId="21" r:id="rId3"/>
+    <sheet name="6.2ГКЛ" sheetId="20" r:id="rId4"/>
+    <sheet name="6.1ГКЛ" sheetId="19" r:id="rId5"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId6"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId7"/>
+    <sheet name="5.1ГКЛ" sheetId="18" r:id="rId8"/>
+    <sheet name="Table 1" sheetId="2" r:id="rId9"/>
+    <sheet name="2расчет" sheetId="9" r:id="rId10"/>
+    <sheet name="3вор" sheetId="4" r:id="rId11"/>
+    <sheet name="общая" sheetId="11" r:id="rId12"/>
+    <sheet name="3пом" sheetId="8" r:id="rId13"/>
+    <sheet name="3расчет" sheetId="6" r:id="rId14"/>
+    <sheet name="3.1-Пт" sheetId="14" r:id="rId15"/>
+    <sheet name="3.1" sheetId="15" r:id="rId16"/>
+    <sheet name="4.1-Пт" sheetId="16" r:id="rId17"/>
+    <sheet name="4.1" sheetId="17" r:id="rId18"/>
+    <sheet name="ПТ3эт" sheetId="12" r:id="rId19"/>
+    <sheet name="ПТ2эт" sheetId="13" r:id="rId20"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="823">
   <si>
     <t>пт-6</t>
   </si>
@@ -9451,7 +9452,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -10020,14 +10021,11 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10035,8 +10033,23 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -10044,10 +10057,13 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10063,31 +10079,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -10879,177 +10874,426 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" style="184" customWidth="1"/>
-    <col min="2" max="2" width="53.21875" style="184" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="184" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="184" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="184" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="184"/>
+    <col min="1" max="1" width="11.33203125" style="184" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" style="184" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" style="184" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" style="184" customWidth="1"/>
+    <col min="5" max="5" width="11" style="184" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="184" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="184"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="205" t="s">
+        <v>787</v>
+      </c>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="185" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="212" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="185" t="s">
+      <c r="C2" s="213"/>
+      <c r="D2" s="203" t="s">
         <v>766</v>
       </c>
-      <c r="D2" s="186" t="s">
+      <c r="E2" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="186" t="s">
+      <c r="F2" s="186" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="206">
+    <row r="3" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="202">
         <v>1</v>
       </c>
-      <c r="B3" s="188" t="s">
-        <v>819</v>
-      </c>
-      <c r="C3" s="222" t="s">
-        <v>818</v>
-      </c>
-      <c r="D3" s="206" t="s">
+      <c r="B3" s="214" t="s">
+        <v>812</v>
+      </c>
+      <c r="C3" s="215"/>
+      <c r="D3" s="204" t="s">
+        <v>813</v>
+      </c>
+      <c r="E3" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="206">
-        <f>3.91+7.12</f>
-        <v>11.030000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="206">
+      <c r="F3" s="202">
+        <f>B14</f>
+        <v>5365.5599999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="202">
         <v>2</v>
       </c>
-      <c r="B4" s="188" t="s">
-        <v>805</v>
-      </c>
-      <c r="C4" s="223"/>
-      <c r="D4" s="206" t="s">
+      <c r="B4" s="214" t="s">
+        <v>812</v>
+      </c>
+      <c r="C4" s="215"/>
+      <c r="D4" s="204" t="s">
+        <v>814</v>
+      </c>
+      <c r="E4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="206">
-        <f>E3</f>
-        <v>11.030000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="206">
+      <c r="F4" s="202">
+        <f>B20</f>
+        <v>118.80000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="202">
         <v>3</v>
       </c>
-      <c r="B5" s="188" t="s">
-        <v>806</v>
-      </c>
-      <c r="C5" s="223"/>
-      <c r="D5" s="206" t="s">
+      <c r="B5" s="214" t="s">
+        <v>812</v>
+      </c>
+      <c r="C5" s="215"/>
+      <c r="D5" s="204" t="s">
+        <v>815</v>
+      </c>
+      <c r="E5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="206">
-        <f>E4</f>
-        <v>11.030000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="206">
+      <c r="F5" s="202">
+        <f>B27</f>
+        <v>2405.2799999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="202">
         <v>4</v>
       </c>
-      <c r="B6" s="188" t="s">
-        <v>822</v>
-      </c>
-      <c r="C6" s="223"/>
-      <c r="D6" s="206" t="s">
+      <c r="B6" s="214" t="s">
+        <v>812</v>
+      </c>
+      <c r="C6" s="215"/>
+      <c r="D6" s="204" t="s">
+        <v>816</v>
+      </c>
+      <c r="E6" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="206">
-        <v>3.91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="206">
+      <c r="F6" s="202">
+        <f>F12</f>
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="202">
         <v>5</v>
       </c>
-      <c r="B7" s="188" t="s">
-        <v>821</v>
-      </c>
-      <c r="C7" s="223"/>
-      <c r="D7" s="206" t="s">
+      <c r="B7" s="214" t="s">
+        <v>812</v>
+      </c>
+      <c r="C7" s="215"/>
+      <c r="D7" s="204" t="s">
+        <v>817</v>
+      </c>
+      <c r="E7" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="206">
-        <v>7.12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="206">
-        <v>6</v>
-      </c>
-      <c r="B8" s="188" t="s">
-        <v>807</v>
-      </c>
-      <c r="C8" s="224"/>
-      <c r="D8" s="206" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="206">
-        <f>C11</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="211"/>
-      <c r="B9" s="211"/>
-      <c r="C9" s="211"/>
-      <c r="D9" s="211"/>
-      <c r="E9" s="218"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="207" t="s">
-        <v>780</v>
-      </c>
-      <c r="B10" s="207"/>
-      <c r="C10" s="207"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="219"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="185" t="s">
-        <v>774</v>
-      </c>
-      <c r="B11" s="185" t="s">
-        <v>820</v>
-      </c>
-      <c r="C11" s="185">
-        <f>3*4*2</f>
-        <v>24</v>
-      </c>
-      <c r="D11" s="206" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="219"/>
+      <c r="F7" s="202">
+        <f>F17</f>
+        <v>240.71999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="205"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="205" t="s">
+        <v>587</v>
+      </c>
+      <c r="B9" s="205"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="205" t="s">
+        <v>664</v>
+      </c>
+      <c r="F9" s="205"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="202" t="s">
+        <v>810</v>
+      </c>
+      <c r="B10" s="202" t="s">
+        <v>811</v>
+      </c>
+      <c r="C10" s="217"/>
+      <c r="D10" s="220"/>
+      <c r="E10" s="202" t="s">
+        <v>810</v>
+      </c>
+      <c r="F10" s="202" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="202">
+        <v>1</v>
+      </c>
+      <c r="B11" s="202">
+        <f>1752.6*1.2</f>
+        <v>2103.12</v>
+      </c>
+      <c r="C11" s="217"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="202">
+        <v>1</v>
+      </c>
+      <c r="F11" s="202">
+        <f>27.1*1.2</f>
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="202">
+        <v>2</v>
+      </c>
+      <c r="B12" s="202">
+        <f>1381.8*1.2</f>
+        <v>1658.1599999999999</v>
+      </c>
+      <c r="C12" s="217"/>
+      <c r="D12" s="220"/>
+      <c r="E12" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="202">
+        <f>SUM(F11:F11)</f>
+        <v>32.520000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="202">
+        <v>3</v>
+      </c>
+      <c r="B13" s="202">
+        <f>1336.9*1.2</f>
+        <v>1604.28</v>
+      </c>
+      <c r="C13" s="217"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="212"/>
+      <c r="F13" s="213"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="202">
+        <f>SUM(B11:B13)</f>
+        <v>5365.5599999999995</v>
+      </c>
+      <c r="C14" s="217"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="205" t="s">
+        <v>591</v>
+      </c>
+      <c r="F14" s="205"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="212"/>
+      <c r="B15" s="213"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="220"/>
+      <c r="E15" s="202" t="s">
+        <v>810</v>
+      </c>
+      <c r="F15" s="202" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="205" t="s">
+        <v>598</v>
+      </c>
+      <c r="B16" s="205"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="202">
+        <v>3</v>
+      </c>
+      <c r="F16" s="202">
+        <f>200.6*1.2</f>
+        <v>240.71999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="202" t="s">
+        <v>810</v>
+      </c>
+      <c r="B17" s="202" t="s">
+        <v>811</v>
+      </c>
+      <c r="C17" s="217"/>
+      <c r="D17" s="220"/>
+      <c r="E17" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="202">
+        <f>SUM(F16:F16)</f>
+        <v>240.71999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="202">
+        <v>1</v>
+      </c>
+      <c r="B18" s="202">
+        <f>60.1*1.2</f>
+        <v>72.12</v>
+      </c>
+      <c r="C18" s="217"/>
+      <c r="D18" s="218"/>
+      <c r="E18" s="218"/>
+      <c r="F18" s="218"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="202">
+        <v>3</v>
+      </c>
+      <c r="B19" s="202">
+        <f>38.9*1.2</f>
+        <v>46.68</v>
+      </c>
+      <c r="C19" s="217"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="218"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="202">
+        <f>SUM(B18:B19)</f>
+        <v>118.80000000000001</v>
+      </c>
+      <c r="C20" s="217"/>
+      <c r="D20" s="218"/>
+      <c r="E20" s="218"/>
+      <c r="F20" s="218"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="212"/>
+      <c r="B21" s="213"/>
+      <c r="C21" s="217"/>
+      <c r="D21" s="218"/>
+      <c r="E21" s="218"/>
+      <c r="F21" s="218"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="205" t="s">
+        <v>678</v>
+      </c>
+      <c r="B22" s="205"/>
+      <c r="C22" s="217"/>
+      <c r="D22" s="218"/>
+      <c r="E22" s="218"/>
+      <c r="F22" s="218"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="202" t="s">
+        <v>810</v>
+      </c>
+      <c r="B23" s="202" t="s">
+        <v>811</v>
+      </c>
+      <c r="C23" s="217"/>
+      <c r="D23" s="218"/>
+      <c r="E23" s="218"/>
+      <c r="F23" s="218"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="202">
+        <v>1</v>
+      </c>
+      <c r="B24" s="202">
+        <f>892.5*1.2</f>
+        <v>1071</v>
+      </c>
+      <c r="C24" s="217"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
+      <c r="F24" s="218"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="202">
+        <v>2</v>
+      </c>
+      <c r="B25" s="202">
+        <f>375.1*1.2</f>
+        <v>450.12</v>
+      </c>
+      <c r="C25" s="217"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
+      <c r="F25" s="218"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="202">
+        <v>3</v>
+      </c>
+      <c r="B26" s="202">
+        <f>736.8*1.2</f>
+        <v>884.16</v>
+      </c>
+      <c r="C26" s="217"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
+      <c r="F26" s="218"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="202">
+        <f>SUM(B24:B26)</f>
+        <v>2405.2799999999997</v>
+      </c>
+      <c r="C27" s="217"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
+      <c r="F27" s="218"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E9:E11"/>
+  <mergeCells count="18">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="E18:F27"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D27"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11057,6 +11301,824 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.44140625" style="46" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="46" customWidth="1"/>
+    <col min="3" max="5" width="9.109375" style="46" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" style="46" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="51"/>
+      <c r="E1" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>2003</v>
+      </c>
+      <c r="B2" s="27">
+        <f>Лист1!B2</f>
+        <v>217.89999999999998</v>
+      </c>
+      <c r="C2" s="27">
+        <v>218.2</v>
+      </c>
+      <c r="D2" s="51"/>
+      <c r="E2" s="27">
+        <v>218.2</v>
+      </c>
+      <c r="F2" s="53">
+        <f>C2-E2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>2009</v>
+      </c>
+      <c r="B3" s="27">
+        <f>Лист1!B3</f>
+        <v>8.9</v>
+      </c>
+      <c r="C3" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="D3" s="51"/>
+      <c r="E3" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="F3" s="53">
+        <f t="shared" ref="F3:F30" si="0">C3-E3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>2010</v>
+      </c>
+      <c r="B4" s="27">
+        <f>Лист1!B4</f>
+        <v>21.6</v>
+      </c>
+      <c r="C4" s="48">
+        <v>23.5</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="48">
+        <v>23.5</v>
+      </c>
+      <c r="F4" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="54">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="55">
+        <f>Лист1!B5</f>
+        <v>236.70000000000002</v>
+      </c>
+      <c r="C5" s="55">
+        <f>478.8</f>
+        <v>478.8</v>
+      </c>
+      <c r="D5" s="56"/>
+      <c r="E5" s="55">
+        <v>237.9</v>
+      </c>
+      <c r="F5" s="57">
+        <f t="shared" si="0"/>
+        <v>240.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>2018</v>
+      </c>
+      <c r="B6" s="27">
+        <f>Лист1!B6</f>
+        <v>18.900000000000002</v>
+      </c>
+      <c r="C6" s="27">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D6" s="51"/>
+      <c r="E6" s="27">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F6" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="27">
+        <f>Лист1!B7</f>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="C7" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="D7" s="51"/>
+      <c r="E7" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="F7" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>2022</v>
+      </c>
+      <c r="B8" s="27">
+        <f>Лист1!B8</f>
+        <v>471.2</v>
+      </c>
+      <c r="C8" s="27">
+        <f>478.7</f>
+        <v>478.7</v>
+      </c>
+      <c r="D8" s="51"/>
+      <c r="E8" s="27">
+        <v>476.6</v>
+      </c>
+      <c r="F8" s="53">
+        <f t="shared" si="0"/>
+        <v>2.0999999999999659</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>2026</v>
+      </c>
+      <c r="B9" s="27">
+        <f>Лист1!B9</f>
+        <v>15.6</v>
+      </c>
+      <c r="C9" s="27">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D9" s="51"/>
+      <c r="E9" s="27">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F9" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>2027</v>
+      </c>
+      <c r="B10" s="27">
+        <f>Лист1!B10</f>
+        <v>7.6</v>
+      </c>
+      <c r="C10" s="27">
+        <v>8.1</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="27">
+        <v>8.1</v>
+      </c>
+      <c r="F10" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>2028</v>
+      </c>
+      <c r="B11" s="27">
+        <f>Лист1!B11</f>
+        <v>19</v>
+      </c>
+      <c r="C11" s="27">
+        <v>19.8</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="27">
+        <v>19.8</v>
+      </c>
+      <c r="F11" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
+        <v>2029</v>
+      </c>
+      <c r="B12" s="27">
+        <f>Лист1!B12</f>
+        <v>7.2999999999999989</v>
+      </c>
+      <c r="C12" s="27">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="27">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F12" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>2032</v>
+      </c>
+      <c r="B13" s="27">
+        <f>Лист1!B13</f>
+        <v>19.5</v>
+      </c>
+      <c r="C13" s="27">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D13" s="51"/>
+      <c r="E13" s="27">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F13" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
+        <v>2042</v>
+      </c>
+      <c r="B14" s="27">
+        <f>Лист1!B14</f>
+        <v>101.8</v>
+      </c>
+      <c r="C14" s="27">
+        <v>103.6</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="27">
+        <v>103.6</v>
+      </c>
+      <c r="F14" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>2043</v>
+      </c>
+      <c r="B15" s="27">
+        <f>Лист1!B15</f>
+        <v>10.3</v>
+      </c>
+      <c r="C15" s="27">
+        <v>10.4</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="27">
+        <v>10.4</v>
+      </c>
+      <c r="F15" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="54">
+        <v>2046</v>
+      </c>
+      <c r="B16" s="55">
+        <f>Лист1!B16</f>
+        <v>162.10000000000002</v>
+      </c>
+      <c r="C16" s="55">
+        <f>326</f>
+        <v>326</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="55">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="F16" s="57">
+        <f t="shared" si="0"/>
+        <v>162.69999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="54">
+        <v>2049</v>
+      </c>
+      <c r="B17" s="55">
+        <f>Лист1!B17</f>
+        <v>127.00000000000001</v>
+      </c>
+      <c r="C17" s="55">
+        <v>256.2</v>
+      </c>
+      <c r="D17" s="56"/>
+      <c r="E17" s="55">
+        <v>128.30000000000001</v>
+      </c>
+      <c r="F17" s="57">
+        <f t="shared" si="0"/>
+        <v>127.89999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
+        <v>2051</v>
+      </c>
+      <c r="B18" s="27">
+        <f>Лист1!B18</f>
+        <v>21.4</v>
+      </c>
+      <c r="C18" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="D18" s="51"/>
+      <c r="E18" s="27">
+        <v>22.2</v>
+      </c>
+      <c r="F18" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
+        <v>2052</v>
+      </c>
+      <c r="B19" s="27">
+        <f>Лист1!B19</f>
+        <v>4</v>
+      </c>
+      <c r="C19" s="27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F19" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
+        <v>2053</v>
+      </c>
+      <c r="B20" s="27">
+        <f>Лист1!B20</f>
+        <v>5.3</v>
+      </c>
+      <c r="C20" s="27">
+        <v>5.6</v>
+      </c>
+      <c r="D20" s="51"/>
+      <c r="E20" s="27">
+        <v>5.6</v>
+      </c>
+      <c r="F20" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
+        <v>2054</v>
+      </c>
+      <c r="B21" s="27">
+        <f>Лист1!B21</f>
+        <v>20.6</v>
+      </c>
+      <c r="C21" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="D21" s="51"/>
+      <c r="E21" s="27">
+        <v>22.1</v>
+      </c>
+      <c r="F21" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
+        <v>2055</v>
+      </c>
+      <c r="B22" s="27">
+        <f>Лист1!B22</f>
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="C22" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="D22" s="51"/>
+      <c r="E22" s="27">
+        <v>10.3</v>
+      </c>
+      <c r="F22" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>2057</v>
+      </c>
+      <c r="B23" s="27">
+        <f>Лист1!B23</f>
+        <v>18</v>
+      </c>
+      <c r="C23" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="D23" s="51"/>
+      <c r="E23" s="27">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="F23" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>2058</v>
+      </c>
+      <c r="B24" s="27">
+        <f>Лист1!B24</f>
+        <v>34.299999999999997</v>
+      </c>
+      <c r="C24" s="27">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="D24" s="51"/>
+      <c r="E24" s="27">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="F24" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="54">
+        <v>2062</v>
+      </c>
+      <c r="B25" s="55">
+        <f>Лист1!B25</f>
+        <v>212.7</v>
+      </c>
+      <c r="C25" s="55">
+        <f>426.5</f>
+        <v>426.5</v>
+      </c>
+      <c r="D25" s="56"/>
+      <c r="E25" s="55">
+        <v>213.5</v>
+      </c>
+      <c r="F25" s="57">
+        <f t="shared" si="0"/>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>2067</v>
+      </c>
+      <c r="B26" s="27">
+        <f>Лист1!B26</f>
+        <v>89.6</v>
+      </c>
+      <c r="C26" s="27">
+        <v>90.8</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="27">
+        <v>90.8</v>
+      </c>
+      <c r="F26" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
+        <v>2068</v>
+      </c>
+      <c r="B27" s="27">
+        <f>Лист1!B27</f>
+        <v>111.8</v>
+      </c>
+      <c r="C27" s="27">
+        <v>112.7</v>
+      </c>
+      <c r="D27" s="51"/>
+      <c r="E27" s="27">
+        <v>112.7</v>
+      </c>
+      <c r="F27" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>2069</v>
+      </c>
+      <c r="B28" s="27">
+        <f>Лист1!B28</f>
+        <v>3.1</v>
+      </c>
+      <c r="C28" s="27">
+        <v>3.2</v>
+      </c>
+      <c r="D28" s="51"/>
+      <c r="E28" s="27">
+        <v>3.2</v>
+      </c>
+      <c r="F28" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>2070</v>
+      </c>
+      <c r="B29" s="27">
+        <f>Лист1!B29</f>
+        <v>13.700000000000001</v>
+      </c>
+      <c r="C29" s="27">
+        <v>15.3</v>
+      </c>
+      <c r="D29" s="51"/>
+      <c r="E29" s="27">
+        <v>15.3</v>
+      </c>
+      <c r="F29" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="54">
+        <v>2071</v>
+      </c>
+      <c r="B30" s="55">
+        <f>Лист1!B30</f>
+        <v>128.1</v>
+      </c>
+      <c r="C30" s="55">
+        <v>257.10000000000002</v>
+      </c>
+      <c r="D30" s="56"/>
+      <c r="E30" s="55">
+        <v>128.9</v>
+      </c>
+      <c r="F30" s="57">
+        <f t="shared" si="0"/>
+        <v>128.20000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="50">
+        <f>SUM(B2:B30)</f>
+        <v>2126.1999999999998</v>
+      </c>
+      <c r="C31" s="50">
+        <f t="shared" ref="C31:E31" si="1">SUM(C2:C30)</f>
+        <v>3034.3</v>
+      </c>
+      <c r="D31" s="50">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="50">
+        <f t="shared" si="1"/>
+        <v>2159.5</v>
+      </c>
+      <c r="F31" s="51"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
+        <v>2008</v>
+      </c>
+      <c r="B33" s="27">
+        <v>57.099999999999994</v>
+      </c>
+      <c r="C33" s="27">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="E33" s="46">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>2019</v>
+      </c>
+      <c r="B34" s="27">
+        <v>55.6</v>
+      </c>
+      <c r="C34" s="27">
+        <f>40.6+15</f>
+        <v>55.6</v>
+      </c>
+      <c r="E34" s="46">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
+        <v>2023</v>
+      </c>
+      <c r="B35" s="27">
+        <v>23.4</v>
+      </c>
+      <c r="C35" s="27">
+        <v>23.4</v>
+      </c>
+      <c r="E35" s="46">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B36" s="27">
+        <v>67.599999999999994</v>
+      </c>
+      <c r="C36" s="27">
+        <f>52.6+15</f>
+        <v>67.599999999999994</v>
+      </c>
+      <c r="E36" s="46">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
+        <v>2044</v>
+      </c>
+      <c r="B37" s="27">
+        <v>63.6</v>
+      </c>
+      <c r="C37" s="27">
+        <f>43.6+20</f>
+        <v>63.6</v>
+      </c>
+      <c r="E37" s="46">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
+        <v>2056</v>
+      </c>
+      <c r="B38" s="27">
+        <v>50.4</v>
+      </c>
+      <c r="C38" s="27">
+        <f>30.4+20</f>
+        <v>50.4</v>
+      </c>
+      <c r="E38" s="46">
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
+        <v>2063</v>
+      </c>
+      <c r="B39" s="27">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C39" s="27">
+        <f>23.4+22.7+20</f>
+        <v>66.099999999999994</v>
+      </c>
+      <c r="E39" s="46">
+        <v>29.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F40" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="47">
+        <f>B23+B24+B25</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="47">
+        <f>SUM(B16:B22)+B28</f>
+        <v>352.10000000000008</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F42" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="47">
+        <f>B14+B15+B30</f>
+        <v>240.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F43" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="G43" s="47">
+        <f>SUM(B8:B13)+B26+B27</f>
+        <v>741.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F44" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="G44" s="47">
+        <f>SUM(B5:B7)+B29</f>
+        <v>278.90000000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F45" s="46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="47">
+        <f>SUM(B2:B4)</f>
+        <v>248.39999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G46" s="47">
+        <f>SUM(G40:G45)</f>
+        <v>2126.2000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G49" s="47">
+        <f>G46-B31</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -11073,13 +12135,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="231" t="s">
+      <c r="A1" s="229" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="232"/>
-      <c r="C1" s="232"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="233"/>
+      <c r="B1" s="230"/>
+      <c r="C1" s="230"/>
+      <c r="D1" s="230"/>
+      <c r="E1" s="231"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
@@ -11206,7 +12268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -16459,15 +17521,15 @@
       <c r="B218" s="124" t="s">
         <v>408</v>
       </c>
-      <c r="C218" s="234" t="s">
+      <c r="C218" s="232" t="s">
         <v>409</v>
       </c>
-      <c r="D218" s="235"/>
-      <c r="E218" s="235"/>
-      <c r="F218" s="235"/>
-      <c r="G218" s="235"/>
-      <c r="H218" s="235"/>
-      <c r="I218" s="235"/>
+      <c r="D218" s="233"/>
+      <c r="E218" s="233"/>
+      <c r="F218" s="233"/>
+      <c r="G218" s="233"/>
+      <c r="H218" s="233"/>
+      <c r="I218" s="233"/>
       <c r="J218" s="143"/>
     </row>
     <row r="219" spans="1:10" ht="51" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
@@ -17779,7 +18841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
@@ -18035,7 +19097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18736,7 +19798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -18809,7 +19871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -18900,7 +19962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -18973,7 +20035,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -19065,7 +20127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -20581,7 +21643,186 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.77734375" style="184" customWidth="1"/>
+    <col min="2" max="2" width="53.21875" style="184" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="184" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="184" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="184" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="184"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="205" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="185" t="s">
+        <v>764</v>
+      </c>
+      <c r="B2" s="185" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="185" t="s">
+        <v>766</v>
+      </c>
+      <c r="D2" s="186" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="186" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="201">
+        <v>1</v>
+      </c>
+      <c r="B3" s="188" t="s">
+        <v>819</v>
+      </c>
+      <c r="C3" s="206" t="s">
+        <v>818</v>
+      </c>
+      <c r="D3" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="201">
+        <f>3.91+7.12</f>
+        <v>11.030000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="201">
+        <v>2</v>
+      </c>
+      <c r="B4" s="188" t="s">
+        <v>805</v>
+      </c>
+      <c r="C4" s="207"/>
+      <c r="D4" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="201">
+        <f>E3</f>
+        <v>11.030000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="201">
+        <v>3</v>
+      </c>
+      <c r="B5" s="188" t="s">
+        <v>806</v>
+      </c>
+      <c r="C5" s="207"/>
+      <c r="D5" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="201">
+        <f>E4</f>
+        <v>11.030000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="201">
+        <v>4</v>
+      </c>
+      <c r="B6" s="188" t="s">
+        <v>822</v>
+      </c>
+      <c r="C6" s="207"/>
+      <c r="D6" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="201">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="201">
+        <v>5</v>
+      </c>
+      <c r="B7" s="188" t="s">
+        <v>821</v>
+      </c>
+      <c r="C7" s="207"/>
+      <c r="D7" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="201">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="201">
+        <v>6</v>
+      </c>
+      <c r="B8" s="188" t="s">
+        <v>807</v>
+      </c>
+      <c r="C8" s="208"/>
+      <c r="D8" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="201">
+        <f>C11</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="209"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="210"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="205" t="s">
+        <v>780</v>
+      </c>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
+      <c r="D10" s="205"/>
+      <c r="E10" s="211"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="185" t="s">
+        <v>774</v>
+      </c>
+      <c r="B11" s="185" t="s">
+        <v>820</v>
+      </c>
+      <c r="C11" s="185">
+        <f>3*4*2</f>
+        <v>24</v>
+      </c>
+      <c r="D11" s="201" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="211"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="E9:E11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.39997558519241921"/>
@@ -22449,7 +23690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -22464,23 +23705,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="205" t="s">
         <v>787</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="185" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="212" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="209"/>
+      <c r="C2" s="213"/>
       <c r="D2" s="203" t="s">
         <v>766</v>
       </c>
@@ -22492,375 +23733,365 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="201">
+      <c r="A3" s="202">
         <v>1</v>
       </c>
-      <c r="B3" s="216" t="s">
+      <c r="B3" s="214" t="s">
         <v>812</v>
       </c>
-      <c r="C3" s="217"/>
-      <c r="D3" s="202" t="s">
+      <c r="C3" s="215"/>
+      <c r="D3" s="204" t="s">
         <v>813</v>
       </c>
-      <c r="E3" s="201" t="s">
+      <c r="E3" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="201">
+      <c r="F3" s="186">
         <f>B14</f>
-        <v>5365.5599999999995</v>
+        <v>6131.73</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="204">
+      <c r="A4" s="202">
         <v>2</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="214" t="s">
         <v>812</v>
       </c>
-      <c r="C4" s="217"/>
-      <c r="D4" s="205" t="s">
+      <c r="C4" s="215"/>
+      <c r="D4" s="204" t="s">
         <v>814</v>
       </c>
-      <c r="E4" s="204" t="s">
+      <c r="E4" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="204">
+      <c r="F4" s="186">
         <f>B20</f>
-        <v>118.80000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="204">
+      <c r="A5" s="202">
         <v>3</v>
       </c>
-      <c r="B5" s="216" t="s">
+      <c r="B5" s="214" t="s">
         <v>812</v>
       </c>
-      <c r="C5" s="217"/>
-      <c r="D5" s="205" t="s">
+      <c r="C5" s="215"/>
+      <c r="D5" s="204" t="s">
         <v>815</v>
       </c>
-      <c r="E5" s="204" t="s">
+      <c r="E5" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="204">
+      <c r="F5" s="186">
         <f>B27</f>
-        <v>2405.2799999999997</v>
+        <v>2236.2049999999999</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="204">
+      <c r="A6" s="202">
         <v>4</v>
       </c>
-      <c r="B6" s="216" t="s">
+      <c r="B6" s="214" t="s">
         <v>812</v>
       </c>
-      <c r="C6" s="217"/>
-      <c r="D6" s="205" t="s">
+      <c r="C6" s="215"/>
+      <c r="D6" s="204" t="s">
         <v>816</v>
       </c>
-      <c r="E6" s="204" t="s">
+      <c r="E6" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="204">
+      <c r="F6" s="186">
         <f>F12</f>
-        <v>32.520000000000003</v>
+        <v>146.6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="204">
+      <c r="A7" s="202">
         <v>5</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="214" t="s">
         <v>812</v>
       </c>
-      <c r="C7" s="217"/>
-      <c r="D7" s="205" t="s">
+      <c r="C7" s="215"/>
+      <c r="D7" s="204" t="s">
         <v>817</v>
       </c>
-      <c r="E7" s="204" t="s">
+      <c r="E7" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="204">
+      <c r="F7" s="186">
         <f>F17</f>
-        <v>240.71999999999997</v>
+        <v>231.97645</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="207"/>
-      <c r="B8" s="207"/>
-      <c r="C8" s="207"/>
-      <c r="D8" s="207"/>
-      <c r="E8" s="207"/>
-      <c r="F8" s="207"/>
+      <c r="A8" s="205"/>
+      <c r="B8" s="205"/>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="205"/>
+      <c r="F8" s="205"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="207" t="s">
+      <c r="A9" s="205" t="s">
         <v>587</v>
       </c>
-      <c r="B9" s="207"/>
-      <c r="C9" s="210"/>
-      <c r="D9" s="214"/>
-      <c r="E9" s="207" t="s">
+      <c r="B9" s="205"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="205" t="s">
         <v>664</v>
       </c>
-      <c r="F9" s="207"/>
+      <c r="F9" s="205"/>
     </row>
     <row r="10" spans="1:6" s="194" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="204" t="s">
+      <c r="A10" s="202" t="s">
         <v>810</v>
       </c>
-      <c r="B10" s="204" t="s">
+      <c r="B10" s="202" t="s">
         <v>811</v>
       </c>
-      <c r="C10" s="212"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="204" t="s">
+      <c r="C10" s="217"/>
+      <c r="D10" s="220"/>
+      <c r="E10" s="202" t="s">
         <v>810</v>
       </c>
-      <c r="F10" s="204" t="s">
+      <c r="F10" s="202" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="204">
+      <c r="A11" s="202">
         <v>1</v>
       </c>
-      <c r="B11" s="204">
-        <f>1752.6*1.2</f>
-        <v>2103.12</v>
-      </c>
-      <c r="C11" s="212"/>
-      <c r="D11" s="215"/>
-      <c r="E11" s="204">
+      <c r="B11" s="202">
+        <f>1750.1+21*(0.3*2+0.4*2)+4.4*(0.45*2+0.5*2)+3.5*(0.95*2+0.5*2)+2.5*(2*0.75+0.3*2)*4+32*(0.8*2+0.35*2)+9.7*(2*0.4+2*0.5)+26*2*(1*2+0.5*2)+86*0.4*4 + 34.4*0.25*4+13.7*2*0.6+11.4*0.9*2+20*2*0.75</f>
+        <v>2305.0299999999997</v>
+      </c>
+      <c r="C11" s="217"/>
+      <c r="D11" s="220"/>
+      <c r="E11" s="202">
         <v>1</v>
       </c>
-      <c r="F11" s="204">
-        <f>27.1*1.2</f>
-        <v>32.520000000000003</v>
+      <c r="F11" s="202">
+        <v>146.6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="204">
+      <c r="A12" s="202">
         <v>2</v>
       </c>
-      <c r="B12" s="204">
-        <f>1381.8*1.2</f>
-        <v>1658.1599999999999</v>
-      </c>
-      <c r="C12" s="212"/>
-      <c r="D12" s="215"/>
-      <c r="E12" s="204" t="s">
+      <c r="B12" s="202">
+        <f>1381.8+554</f>
+        <v>1935.8</v>
+      </c>
+      <c r="C12" s="217"/>
+      <c r="D12" s="220"/>
+      <c r="E12" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="204">
+      <c r="F12" s="202">
         <f>SUM(F11:F11)</f>
-        <v>32.520000000000003</v>
+        <v>146.6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="204">
+      <c r="A13" s="202">
         <v>3</v>
       </c>
-      <c r="B13" s="204">
-        <f>1336.9*1.2</f>
-        <v>1604.28</v>
-      </c>
-      <c r="C13" s="212"/>
-      <c r="D13" s="215"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="209"/>
+      <c r="B13" s="202">
+        <f>1336.9+554</f>
+        <v>1890.9</v>
+      </c>
+      <c r="C13" s="217"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="212"/>
+      <c r="F13" s="213"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="204" t="s">
+      <c r="A14" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="204">
+      <c r="B14" s="202">
         <f>SUM(B11:B13)</f>
-        <v>5365.5599999999995</v>
-      </c>
-      <c r="C14" s="212"/>
-      <c r="D14" s="215"/>
-      <c r="E14" s="207" t="s">
+        <v>6131.73</v>
+      </c>
+      <c r="C14" s="217"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="205" t="s">
         <v>591</v>
       </c>
-      <c r="F14" s="207"/>
+      <c r="F14" s="205"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="208"/>
-      <c r="B15" s="209"/>
-      <c r="C15" s="212"/>
-      <c r="D15" s="215"/>
-      <c r="E15" s="204" t="s">
+      <c r="A15" s="212"/>
+      <c r="B15" s="213"/>
+      <c r="C15" s="217"/>
+      <c r="D15" s="220"/>
+      <c r="E15" s="202" t="s">
         <v>810</v>
       </c>
-      <c r="F15" s="204" t="s">
+      <c r="F15" s="202" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="207" t="s">
+      <c r="A16" s="205" t="s">
         <v>598</v>
       </c>
-      <c r="B16" s="207"/>
-      <c r="C16" s="212"/>
-      <c r="D16" s="215"/>
-      <c r="E16" s="204">
+      <c r="B16" s="205"/>
+      <c r="C16" s="217"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="202">
         <v>3</v>
       </c>
-      <c r="F16" s="204">
-        <f>200.6*1.2</f>
-        <v>240.71999999999997</v>
+      <c r="F16" s="186">
+        <f>200.6+7.4*0.2*3.14+5.7*0.25*3.14+22.5*3.14*0.315</f>
+        <v>231.97645</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="204" t="s">
+      <c r="A17" s="202" t="s">
         <v>810</v>
       </c>
-      <c r="B17" s="204" t="s">
+      <c r="B17" s="202" t="s">
         <v>811</v>
       </c>
-      <c r="C17" s="212"/>
-      <c r="D17" s="215"/>
-      <c r="E17" s="204" t="s">
+      <c r="C17" s="217"/>
+      <c r="D17" s="220"/>
+      <c r="E17" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="204">
+      <c r="F17" s="186">
         <f>SUM(F16:F16)</f>
-        <v>240.71999999999997</v>
+        <v>231.97645</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="204">
+      <c r="A18" s="202">
         <v>1</v>
       </c>
-      <c r="B18" s="204">
-        <f>60.1*1.2</f>
-        <v>72.12</v>
-      </c>
-      <c r="C18" s="212"/>
-      <c r="D18" s="215"/>
-      <c r="E18" s="210"/>
-      <c r="F18" s="211"/>
+      <c r="B18" s="202">
+        <v>48.1</v>
+      </c>
+      <c r="C18" s="217"/>
+      <c r="D18" s="218"/>
+      <c r="E18" s="218"/>
+      <c r="F18" s="218"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="204">
+      <c r="A19" s="202">
         <v>3</v>
       </c>
-      <c r="B19" s="204">
-        <f>38.9*1.2</f>
-        <v>46.68</v>
-      </c>
-      <c r="C19" s="212"/>
-      <c r="D19" s="215"/>
-      <c r="E19" s="212"/>
-      <c r="F19" s="213"/>
+      <c r="B19" s="202">
+        <f>38.9</f>
+        <v>38.9</v>
+      </c>
+      <c r="C19" s="217"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="218"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="204" t="s">
+      <c r="A20" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="204">
+      <c r="B20" s="202">
         <f>SUM(B18:B19)</f>
-        <v>118.80000000000001</v>
-      </c>
-      <c r="C20" s="212"/>
-      <c r="D20" s="215"/>
-      <c r="E20" s="212"/>
-      <c r="F20" s="213"/>
+        <v>87</v>
+      </c>
+      <c r="C20" s="217"/>
+      <c r="D20" s="218"/>
+      <c r="E20" s="218"/>
+      <c r="F20" s="218"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="208"/>
-      <c r="B21" s="209"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="215"/>
-      <c r="E21" s="212"/>
-      <c r="F21" s="213"/>
+      <c r="A21" s="212"/>
+      <c r="B21" s="213"/>
+      <c r="C21" s="217"/>
+      <c r="D21" s="218"/>
+      <c r="E21" s="218"/>
+      <c r="F21" s="218"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="207" t="s">
+      <c r="A22" s="205" t="s">
         <v>678</v>
       </c>
-      <c r="B22" s="207"/>
-      <c r="C22" s="212"/>
-      <c r="D22" s="215"/>
-      <c r="E22" s="212"/>
-      <c r="F22" s="213"/>
+      <c r="B22" s="205"/>
+      <c r="C22" s="217"/>
+      <c r="D22" s="218"/>
+      <c r="E22" s="218"/>
+      <c r="F22" s="218"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="204" t="s">
+      <c r="A23" s="202" t="s">
         <v>810</v>
       </c>
-      <c r="B23" s="204" t="s">
+      <c r="B23" s="202" t="s">
         <v>811</v>
       </c>
-      <c r="C23" s="212"/>
-      <c r="D23" s="215"/>
-      <c r="E23" s="212"/>
-      <c r="F23" s="213"/>
+      <c r="C23" s="217"/>
+      <c r="D23" s="218"/>
+      <c r="E23" s="218"/>
+      <c r="F23" s="218"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="204">
+      <c r="A24" s="202">
         <v>1</v>
       </c>
-      <c r="B24" s="204">
-        <f>892.5*1.2</f>
-        <v>1071</v>
-      </c>
-      <c r="C24" s="212"/>
-      <c r="D24" s="215"/>
-      <c r="E24" s="212"/>
-      <c r="F24" s="213"/>
+      <c r="B24" s="202">
+        <f>892.54+3.14*0.4*(10+6)*5</f>
+        <v>993.02</v>
+      </c>
+      <c r="C24" s="217"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
+      <c r="F24" s="218"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="204">
+      <c r="A25" s="202">
         <v>2</v>
       </c>
-      <c r="B25" s="204">
-        <f>375.1*1.2</f>
-        <v>450.12</v>
-      </c>
-      <c r="C25" s="212"/>
-      <c r="D25" s="215"/>
-      <c r="E25" s="212"/>
-      <c r="F25" s="213"/>
+      <c r="B25" s="202">
+        <f>375.1*1.35</f>
+        <v>506.38500000000005</v>
+      </c>
+      <c r="C25" s="217"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
+      <c r="F25" s="218"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="204">
+      <c r="A26" s="202">
         <v>3</v>
       </c>
-      <c r="B26" s="204">
-        <f>736.8*1.2</f>
-        <v>884.16</v>
-      </c>
-      <c r="C26" s="212"/>
-      <c r="D26" s="215"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="213"/>
+      <c r="B26" s="202">
+        <f>736.8</f>
+        <v>736.8</v>
+      </c>
+      <c r="C26" s="217"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
+      <c r="F26" s="218"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="204" t="s">
+      <c r="A27" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="204">
+      <c r="B27" s="202">
         <f>SUM(B24:B26)</f>
-        <v>2405.2799999999997</v>
-      </c>
-      <c r="C27" s="212"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="212"/>
-      <c r="F27" s="213"/>
+        <v>2236.2049999999999</v>
+      </c>
+      <c r="C27" s="217"/>
+      <c r="D27" s="218"/>
+      <c r="E27" s="218"/>
+      <c r="F27" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="E9:F9"/>
@@ -22871,13 +24102,21 @@
     <mergeCell ref="E18:F27"/>
     <mergeCell ref="C9:D27"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -22891,12 +24130,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="185" t="s">
@@ -22922,7 +24161,7 @@
       <c r="B3" s="188" t="s">
         <v>809</v>
       </c>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="206" t="s">
         <v>808</v>
       </c>
       <c r="D3" s="196" t="s">
@@ -22939,7 +24178,7 @@
       <c r="B4" s="188" t="s">
         <v>805</v>
       </c>
-      <c r="C4" s="223"/>
+      <c r="C4" s="207"/>
       <c r="D4" s="196" t="s">
         <v>7</v>
       </c>
@@ -22954,7 +24193,7 @@
       <c r="B5" s="188" t="s">
         <v>806</v>
       </c>
-      <c r="C5" s="223"/>
+      <c r="C5" s="207"/>
       <c r="D5" s="196" t="s">
         <v>7</v>
       </c>
@@ -22970,7 +24209,7 @@
       <c r="B6" s="188" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="223"/>
+      <c r="C6" s="207"/>
       <c r="D6" s="196" t="s">
         <v>7</v>
       </c>
@@ -22986,7 +24225,7 @@
       <c r="B7" s="188" t="s">
         <v>807</v>
       </c>
-      <c r="C7" s="224"/>
+      <c r="C7" s="208"/>
       <c r="D7" s="196" t="s">
         <v>7</v>
       </c>
@@ -22996,20 +24235,20 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="211"/>
-      <c r="B8" s="211"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="218"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="210"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="207" t="s">
+      <c r="A9" s="205" t="s">
         <v>802</v>
       </c>
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-      <c r="D9" s="207"/>
-      <c r="E9" s="219"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="211"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="198">
@@ -23024,7 +24263,7 @@
       <c r="D10" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="219"/>
+      <c r="E10" s="211"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="198">
@@ -23039,7 +24278,7 @@
       <c r="D11" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="219"/>
+      <c r="E11" s="211"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="198">
@@ -23054,7 +24293,7 @@
       <c r="D12" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="219"/>
+      <c r="E12" s="211"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="198">
@@ -23069,13 +24308,13 @@
       <c r="D13" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="219"/>
+      <c r="E13" s="211"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="220" t="s">
+      <c r="A14" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="221"/>
+      <c r="B14" s="222"/>
       <c r="C14" s="198">
         <f>SUM(C10:C13)</f>
         <v>17.62</v>
@@ -23083,23 +24322,23 @@
       <c r="D14" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="219"/>
+      <c r="E14" s="211"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="219"/>
+      <c r="A15" s="209"/>
+      <c r="B15" s="209"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="209"/>
+      <c r="E15" s="211"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="207" t="s">
+      <c r="A16" s="205" t="s">
         <v>801</v>
       </c>
-      <c r="B16" s="207"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="219"/>
+      <c r="B16" s="205"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="211"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="198">
@@ -23114,16 +24353,16 @@
       <c r="D17" s="197" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="219"/>
+      <c r="E17" s="211"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="207" t="s">
+      <c r="A18" s="205" t="s">
         <v>803</v>
       </c>
-      <c r="B18" s="207"/>
-      <c r="C18" s="207"/>
-      <c r="D18" s="207"/>
-      <c r="E18" s="219"/>
+      <c r="B18" s="205"/>
+      <c r="C18" s="205"/>
+      <c r="D18" s="205"/>
+      <c r="E18" s="211"/>
     </row>
     <row r="19" spans="1:5" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="198">
@@ -23139,23 +24378,23 @@
       <c r="D19" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="219"/>
+      <c r="E19" s="211"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="211"/>
-      <c r="B20" s="211"/>
-      <c r="C20" s="211"/>
-      <c r="D20" s="211"/>
-      <c r="E20" s="219"/>
+      <c r="A20" s="209"/>
+      <c r="B20" s="209"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="209"/>
+      <c r="E20" s="211"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="207" t="s">
+      <c r="A21" s="205" t="s">
         <v>780</v>
       </c>
-      <c r="B21" s="207"/>
-      <c r="C21" s="207"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="219"/>
+      <c r="B21" s="205"/>
+      <c r="C21" s="205"/>
+      <c r="D21" s="205"/>
+      <c r="E21" s="211"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="185" t="s">
@@ -23170,7 +24409,7 @@
       <c r="D22" s="196" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="219"/>
+      <c r="E22" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -23191,7 +24430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23207,25 +24446,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="205" t="s">
         <v>787</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="205"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="185" t="s">
         <v>764</v>
       </c>
-      <c r="B2" s="208" t="s">
+      <c r="B2" s="212" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="226"/>
-      <c r="D2" s="209"/>
+      <c r="C2" s="224"/>
+      <c r="D2" s="213"/>
       <c r="E2" s="193" t="s">
         <v>766</v>
       </c>
@@ -23240,11 +24479,11 @@
       <c r="A3" s="190">
         <v>1</v>
       </c>
-      <c r="B3" s="216" t="s">
+      <c r="B3" s="214" t="s">
         <v>792</v>
       </c>
-      <c r="C3" s="225"/>
-      <c r="D3" s="217"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="215"/>
       <c r="E3" s="192" t="s">
         <v>791</v>
       </c>
@@ -23260,11 +24499,11 @@
       <c r="A4" s="191">
         <v>2</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="214" t="s">
         <v>788</v>
       </c>
-      <c r="C4" s="225"/>
-      <c r="D4" s="217"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="215"/>
       <c r="E4" s="192" t="s">
         <v>793</v>
       </c>
@@ -23280,11 +24519,11 @@
       <c r="A5" s="191">
         <v>3</v>
       </c>
-      <c r="B5" s="216" t="s">
+      <c r="B5" s="214" t="s">
         <v>788</v>
       </c>
-      <c r="C5" s="225"/>
-      <c r="D5" s="217"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="215"/>
       <c r="E5" s="192" t="s">
         <v>794</v>
       </c>
@@ -23300,11 +24539,11 @@
       <c r="A6" s="191">
         <v>4</v>
       </c>
-      <c r="B6" s="216" t="s">
+      <c r="B6" s="214" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="225"/>
-      <c r="D6" s="217"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="215"/>
       <c r="E6" s="192" t="s">
         <v>789</v>
       </c>
@@ -23320,11 +24559,11 @@
       <c r="A7" s="191">
         <v>5</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="214" t="s">
         <v>772</v>
       </c>
-      <c r="C7" s="225"/>
-      <c r="D7" s="217"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="215"/>
       <c r="E7" s="192" t="s">
         <v>790</v>
       </c>
@@ -23337,13 +24576,13 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="211"/>
-      <c r="B8" s="211"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="211"/>
-      <c r="F8" s="211"/>
-      <c r="G8" s="211"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
     </row>
     <row r="9" spans="1:7" s="194" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="190" t="s">
@@ -23355,10 +24594,10 @@
       <c r="C9" s="190" t="s">
         <v>786</v>
       </c>
-      <c r="D9" s="212"/>
-      <c r="E9" s="213"/>
-      <c r="F9" s="213"/>
-      <c r="G9" s="213"/>
+      <c r="D9" s="217"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="218"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="190">
@@ -23370,10 +24609,10 @@
       <c r="C10" s="195">
         <v>11.22</v>
       </c>
-      <c r="D10" s="212"/>
-      <c r="E10" s="213"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="213"/>
+      <c r="D10" s="217"/>
+      <c r="E10" s="218"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="218"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="190">
@@ -23385,10 +24624,10 @@
       <c r="C11" s="195">
         <v>11.23</v>
       </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="213"/>
+      <c r="D11" s="217"/>
+      <c r="E11" s="218"/>
+      <c r="F11" s="218"/>
+      <c r="G11" s="218"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="190">
@@ -23400,10 +24639,10 @@
       <c r="C12" s="195">
         <v>11.25</v>
       </c>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="213"/>
+      <c r="D12" s="217"/>
+      <c r="E12" s="218"/>
+      <c r="F12" s="218"/>
+      <c r="G12" s="218"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="190">
@@ -23415,10 +24654,10 @@
       <c r="C13" s="195">
         <v>10.130000000000001</v>
       </c>
-      <c r="D13" s="212"/>
-      <c r="E13" s="213"/>
-      <c r="F13" s="213"/>
-      <c r="G13" s="213"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="218"/>
+      <c r="F13" s="218"/>
+      <c r="G13" s="218"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="190">
@@ -23430,10 +24669,10 @@
       <c r="C14" s="195">
         <v>10.130000000000001</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="213"/>
-      <c r="G14" s="213"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="218"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="190">
@@ -23445,10 +24684,10 @@
       <c r="C15" s="195">
         <v>10.14</v>
       </c>
-      <c r="D15" s="212"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="213"/>
-      <c r="G15" s="213"/>
+      <c r="D15" s="217"/>
+      <c r="E15" s="218"/>
+      <c r="F15" s="218"/>
+      <c r="G15" s="218"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="190">
@@ -23460,10 +24699,10 @@
       <c r="C16" s="195">
         <v>8.9</v>
       </c>
-      <c r="D16" s="212"/>
-      <c r="E16" s="213"/>
-      <c r="F16" s="213"/>
-      <c r="G16" s="213"/>
+      <c r="D16" s="217"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="218"/>
+      <c r="G16" s="218"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="190">
@@ -23475,10 +24714,10 @@
       <c r="C17" s="195">
         <v>8.9</v>
       </c>
-      <c r="D17" s="212"/>
-      <c r="E17" s="213"/>
-      <c r="F17" s="213"/>
-      <c r="G17" s="213"/>
+      <c r="D17" s="217"/>
+      <c r="E17" s="218"/>
+      <c r="F17" s="218"/>
+      <c r="G17" s="218"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="190">
@@ -23490,24 +24729,24 @@
       <c r="C18" s="195">
         <v>8.9</v>
       </c>
-      <c r="D18" s="212"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="213"/>
+      <c r="D18" s="217"/>
+      <c r="E18" s="218"/>
+      <c r="F18" s="218"/>
+      <c r="G18" s="218"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="220" t="s">
+      <c r="A19" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="221"/>
+      <c r="B19" s="222"/>
       <c r="C19" s="185">
         <f>SUM(C10:C18)</f>
         <v>90.800000000000026</v>
       </c>
-      <c r="D19" s="212"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="213"/>
+      <c r="D19" s="217"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="218"/>
+      <c r="G19" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23527,7 +24766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
@@ -23544,13 +24783,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="227" t="s">
+      <c r="A1" s="225" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="229"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="227"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -23678,7 +24917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
@@ -23942,7 +25181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -23957,14 +25196,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="205"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="185" t="s">
@@ -24096,22 +25335,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="211"/>
-      <c r="B8" s="211"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="211"/>
-      <c r="E8" s="211"/>
-      <c r="F8" s="211"/>
+      <c r="A8" s="209"/>
+      <c r="B8" s="209"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="207" t="s">
+      <c r="A9" s="205" t="s">
         <v>780</v>
       </c>
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-      <c r="D9" s="207"/>
-      <c r="E9" s="230"/>
-      <c r="F9" s="219"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="228"/>
+      <c r="F9" s="211"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="185" t="s">
@@ -24127,8 +25366,8 @@
       <c r="D10" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="230"/>
-      <c r="F10" s="219"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="211"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="185" t="s">
@@ -24144,8 +25383,8 @@
       <c r="D11" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="230"/>
-      <c r="F11" s="219"/>
+      <c r="E11" s="228"/>
+      <c r="F11" s="211"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="185" t="s">
@@ -24161,8 +25400,8 @@
       <c r="D12" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="230"/>
-      <c r="F12" s="219"/>
+      <c r="E12" s="228"/>
+      <c r="F12" s="211"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="185" t="s">
@@ -24178,14 +25417,14 @@
       <c r="D13" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="230"/>
-      <c r="F13" s="219"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="211"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="220" t="s">
+      <c r="A14" s="221" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="221"/>
+      <c r="B14" s="222"/>
       <c r="C14" s="185">
         <f>SUM(C10:C13)</f>
         <v>280</v>
@@ -24193,8 +25432,8 @@
       <c r="D14" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="230"/>
-      <c r="F14" s="219"/>
+      <c r="E14" s="228"/>
+      <c r="F14" s="211"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -24209,7 +25448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
@@ -27370,822 +28609,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.44140625" style="46" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" style="46" customWidth="1"/>
-    <col min="3" max="5" width="9.109375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" style="46" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="46"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="51"/>
-      <c r="E1" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
-        <v>2003</v>
-      </c>
-      <c r="B2" s="27">
-        <f>Лист1!B2</f>
-        <v>217.89999999999998</v>
-      </c>
-      <c r="C2" s="27">
-        <v>218.2</v>
-      </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="27">
-        <v>218.2</v>
-      </c>
-      <c r="F2" s="53">
-        <f>C2-E2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>2009</v>
-      </c>
-      <c r="B3" s="27">
-        <f>Лист1!B3</f>
-        <v>8.9</v>
-      </c>
-      <c r="C3" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="F3" s="53">
-        <f t="shared" ref="F3:F30" si="0">C3-E3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>2010</v>
-      </c>
-      <c r="B4" s="27">
-        <f>Лист1!B4</f>
-        <v>21.6</v>
-      </c>
-      <c r="C4" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="48">
-        <v>23.5</v>
-      </c>
-      <c r="F4" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="54">
-        <v>2017</v>
-      </c>
-      <c r="B5" s="55">
-        <f>Лист1!B5</f>
-        <v>236.70000000000002</v>
-      </c>
-      <c r="C5" s="55">
-        <f>478.8</f>
-        <v>478.8</v>
-      </c>
-      <c r="D5" s="56"/>
-      <c r="E5" s="55">
-        <v>237.9</v>
-      </c>
-      <c r="F5" s="57">
-        <f t="shared" si="0"/>
-        <v>240.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>2018</v>
-      </c>
-      <c r="B6" s="27">
-        <f>Лист1!B6</f>
-        <v>18.900000000000002</v>
-      </c>
-      <c r="C6" s="27">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="27">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="F6" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="27">
-        <f>Лист1!B7</f>
-        <v>9.6000000000000014</v>
-      </c>
-      <c r="C7" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="F7" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>2022</v>
-      </c>
-      <c r="B8" s="27">
-        <f>Лист1!B8</f>
-        <v>471.2</v>
-      </c>
-      <c r="C8" s="27">
-        <f>478.7</f>
-        <v>478.7</v>
-      </c>
-      <c r="D8" s="51"/>
-      <c r="E8" s="27">
-        <v>476.6</v>
-      </c>
-      <c r="F8" s="53">
-        <f t="shared" si="0"/>
-        <v>2.0999999999999659</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>2026</v>
-      </c>
-      <c r="B9" s="27">
-        <f>Лист1!B9</f>
-        <v>15.6</v>
-      </c>
-      <c r="C9" s="27">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="27">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="F9" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>2027</v>
-      </c>
-      <c r="B10" s="27">
-        <f>Лист1!B10</f>
-        <v>7.6</v>
-      </c>
-      <c r="C10" s="27">
-        <v>8.1</v>
-      </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="27">
-        <v>8.1</v>
-      </c>
-      <c r="F10" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>2028</v>
-      </c>
-      <c r="B11" s="27">
-        <f>Лист1!B11</f>
-        <v>19</v>
-      </c>
-      <c r="C11" s="27">
-        <v>19.8</v>
-      </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="27">
-        <v>19.8</v>
-      </c>
-      <c r="F11" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>2029</v>
-      </c>
-      <c r="B12" s="27">
-        <f>Лист1!B12</f>
-        <v>7.2999999999999989</v>
-      </c>
-      <c r="C12" s="27">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="27">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F12" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
-        <v>2032</v>
-      </c>
-      <c r="B13" s="27">
-        <f>Лист1!B13</f>
-        <v>19.5</v>
-      </c>
-      <c r="C13" s="27">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="27">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="F13" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
-        <v>2042</v>
-      </c>
-      <c r="B14" s="27">
-        <f>Лист1!B14</f>
-        <v>101.8</v>
-      </c>
-      <c r="C14" s="27">
-        <v>103.6</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="27">
-        <v>103.6</v>
-      </c>
-      <c r="F14" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
-        <v>2043</v>
-      </c>
-      <c r="B15" s="27">
-        <f>Лист1!B15</f>
-        <v>10.3</v>
-      </c>
-      <c r="C15" s="27">
-        <v>10.4</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="27">
-        <v>10.4</v>
-      </c>
-      <c r="F15" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="54">
-        <v>2046</v>
-      </c>
-      <c r="B16" s="55">
-        <f>Лист1!B16</f>
-        <v>162.10000000000002</v>
-      </c>
-      <c r="C16" s="55">
-        <f>326</f>
-        <v>326</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="55">
-        <v>163.30000000000001</v>
-      </c>
-      <c r="F16" s="57">
-        <f t="shared" si="0"/>
-        <v>162.69999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="54">
-        <v>2049</v>
-      </c>
-      <c r="B17" s="55">
-        <f>Лист1!B17</f>
-        <v>127.00000000000001</v>
-      </c>
-      <c r="C17" s="55">
-        <v>256.2</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="55">
-        <v>128.30000000000001</v>
-      </c>
-      <c r="F17" s="57">
-        <f t="shared" si="0"/>
-        <v>127.89999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
-        <v>2051</v>
-      </c>
-      <c r="B18" s="27">
-        <f>Лист1!B18</f>
-        <v>21.4</v>
-      </c>
-      <c r="C18" s="27">
-        <v>22.2</v>
-      </c>
-      <c r="D18" s="51"/>
-      <c r="E18" s="27">
-        <v>22.2</v>
-      </c>
-      <c r="F18" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
-        <v>2052</v>
-      </c>
-      <c r="B19" s="27">
-        <f>Лист1!B19</f>
-        <v>4</v>
-      </c>
-      <c r="C19" s="27">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="27">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F19" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
-        <v>2053</v>
-      </c>
-      <c r="B20" s="27">
-        <f>Лист1!B20</f>
-        <v>5.3</v>
-      </c>
-      <c r="C20" s="27">
-        <v>5.6</v>
-      </c>
-      <c r="D20" s="51"/>
-      <c r="E20" s="27">
-        <v>5.6</v>
-      </c>
-      <c r="F20" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
-        <v>2054</v>
-      </c>
-      <c r="B21" s="27">
-        <f>Лист1!B21</f>
-        <v>20.6</v>
-      </c>
-      <c r="C21" s="27">
-        <v>22.1</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="27">
-        <v>22.1</v>
-      </c>
-      <c r="F21" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
-        <v>2055</v>
-      </c>
-      <c r="B22" s="27">
-        <f>Лист1!B22</f>
-        <v>8.6000000000000014</v>
-      </c>
-      <c r="C22" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="27">
-        <v>10.3</v>
-      </c>
-      <c r="F22" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
-        <v>2057</v>
-      </c>
-      <c r="B23" s="27">
-        <f>Лист1!B23</f>
-        <v>18</v>
-      </c>
-      <c r="C23" s="27">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="27">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="F23" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="12">
-        <v>2058</v>
-      </c>
-      <c r="B24" s="27">
-        <f>Лист1!B24</f>
-        <v>34.299999999999997</v>
-      </c>
-      <c r="C24" s="27">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="D24" s="51"/>
-      <c r="E24" s="27">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="F24" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="54">
-        <v>2062</v>
-      </c>
-      <c r="B25" s="55">
-        <f>Лист1!B25</f>
-        <v>212.7</v>
-      </c>
-      <c r="C25" s="55">
-        <f>426.5</f>
-        <v>426.5</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="55">
-        <v>213.5</v>
-      </c>
-      <c r="F25" s="57">
-        <f t="shared" si="0"/>
-        <v>213</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12">
-        <v>2067</v>
-      </c>
-      <c r="B26" s="27">
-        <f>Лист1!B26</f>
-        <v>89.6</v>
-      </c>
-      <c r="C26" s="27">
-        <v>90.8</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="27">
-        <v>90.8</v>
-      </c>
-      <c r="F26" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="12">
-        <v>2068</v>
-      </c>
-      <c r="B27" s="27">
-        <f>Лист1!B27</f>
-        <v>111.8</v>
-      </c>
-      <c r="C27" s="27">
-        <v>112.7</v>
-      </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="27">
-        <v>112.7</v>
-      </c>
-      <c r="F27" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
-        <v>2069</v>
-      </c>
-      <c r="B28" s="27">
-        <f>Лист1!B28</f>
-        <v>3.1</v>
-      </c>
-      <c r="C28" s="27">
-        <v>3.2</v>
-      </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="27">
-        <v>3.2</v>
-      </c>
-      <c r="F28" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="12">
-        <v>2070</v>
-      </c>
-      <c r="B29" s="27">
-        <f>Лист1!B29</f>
-        <v>13.700000000000001</v>
-      </c>
-      <c r="C29" s="27">
-        <v>15.3</v>
-      </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="27">
-        <v>15.3</v>
-      </c>
-      <c r="F29" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="54">
-        <v>2071</v>
-      </c>
-      <c r="B30" s="55">
-        <f>Лист1!B30</f>
-        <v>128.1</v>
-      </c>
-      <c r="C30" s="55">
-        <v>257.10000000000002</v>
-      </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="55">
-        <v>128.9</v>
-      </c>
-      <c r="F30" s="57">
-        <f t="shared" si="0"/>
-        <v>128.20000000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="50">
-        <f>SUM(B2:B30)</f>
-        <v>2126.1999999999998</v>
-      </c>
-      <c r="C31" s="50">
-        <f t="shared" ref="C31:E31" si="1">SUM(C2:C30)</f>
-        <v>3034.3</v>
-      </c>
-      <c r="D31" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E31" s="50">
-        <f t="shared" si="1"/>
-        <v>2159.5</v>
-      </c>
-      <c r="F31" s="51"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="12">
-        <v>2008</v>
-      </c>
-      <c r="B33" s="27">
-        <v>57.099999999999994</v>
-      </c>
-      <c r="C33" s="27">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="E33" s="46">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
-        <v>2019</v>
-      </c>
-      <c r="B34" s="27">
-        <v>55.6</v>
-      </c>
-      <c r="C34" s="27">
-        <f>40.6+15</f>
-        <v>55.6</v>
-      </c>
-      <c r="E34" s="46">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="12">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="27">
-        <v>23.4</v>
-      </c>
-      <c r="C35" s="27">
-        <v>23.4</v>
-      </c>
-      <c r="E35" s="46">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="12">
-        <v>2024</v>
-      </c>
-      <c r="B36" s="27">
-        <v>67.599999999999994</v>
-      </c>
-      <c r="C36" s="27">
-        <f>52.6+15</f>
-        <v>67.599999999999994</v>
-      </c>
-      <c r="E36" s="46">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="12">
-        <v>2044</v>
-      </c>
-      <c r="B37" s="27">
-        <v>63.6</v>
-      </c>
-      <c r="C37" s="27">
-        <f>43.6+20</f>
-        <v>63.6</v>
-      </c>
-      <c r="E37" s="46">
-        <v>34.700000000000003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="12">
-        <v>2056</v>
-      </c>
-      <c r="B38" s="27">
-        <v>50.4</v>
-      </c>
-      <c r="C38" s="27">
-        <f>30.4+20</f>
-        <v>50.4</v>
-      </c>
-      <c r="E38" s="46">
-        <v>33.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="12">
-        <v>2063</v>
-      </c>
-      <c r="B39" s="27">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="C39" s="27">
-        <f>23.4+22.7+20</f>
-        <v>66.099999999999994</v>
-      </c>
-      <c r="E39" s="46">
-        <v>29.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F40" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G40" s="47">
-        <f>B23+B24+B25</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="G41" s="47">
-        <f>SUM(B16:B22)+B28</f>
-        <v>352.10000000000008</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F42" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="47">
-        <f>B14+B15+B30</f>
-        <v>240.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F43" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="G43" s="47">
-        <f>SUM(B8:B13)+B26+B27</f>
-        <v>741.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F44" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="G44" s="47">
-        <f>SUM(B5:B7)+B29</f>
-        <v>278.90000000000003</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F45" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="G45" s="47">
-        <f>SUM(B2:B4)</f>
-        <v>248.39999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G46" s="47">
-        <f>SUM(G40:G45)</f>
-        <v>2126.2000000000003</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G47" s="46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G49" s="47">
-        <f>G46-B31</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>